--- a/data/diabetes korea (GBD).xlsx
+++ b/data/diabetes korea (GBD).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAEC664-842D-D245-822F-27C2EEA519D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5D6F20-C389-E144-ABC2-61940C9B94FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="1800" windowWidth="14160" windowHeight="15760" xr2:uid="{C4FC9700-678B-FA47-80D7-8DB9D2296252}"/>
+    <workbookView xWindow="14280" yWindow="920" windowWidth="14160" windowHeight="15760" xr2:uid="{C4FC9700-678B-FA47-80D7-8DB9D2296252}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -477,16 +477,16 @@
         <v>0.06</v>
       </c>
       <c r="D2">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="E2">
         <v>0.43</v>
       </c>
       <c r="F2">
-        <v>1.1399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H2">
         <v>5058</v>
@@ -500,19 +500,19 @@
         <v>0.02</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D3">
-        <v>0.22</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E3">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="F3">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="G3">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="H3">
         <v>8084</v>
